--- a/13155_Intercuenca_13155/_raw_reportes_xlsx/IDConfig_252_completo.xlsx
+++ b/13155_Intercuenca_13155/_raw_reportes_xlsx/IDConfig_252_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R9935c0914c764a96"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R03e36d7e3564420e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,126 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.5260</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.5920</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.6310</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.5450</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.5240</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4920</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.5240</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.5240</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>11/08/2026</x:t>
         </x:is>
       </x:c>

--- a/13155_Intercuenca_13155/_raw_reportes_xlsx/IDConfig_252_completo.xlsx
+++ b/13155_Intercuenca_13155/_raw_reportes_xlsx/IDConfig_252_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R03e36d7e3564420e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R74e24506ddb64f06"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,756 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8850</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8080</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8210</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8490</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.7280</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.6280</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8530</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9170</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8580</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8880</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8590</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8720</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.7510</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.7510</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9520</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.7420</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8030</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9310</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8460</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.6500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.7020</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.6780</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.6770</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.6310</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.6080</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.7310</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9170</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9030</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9170</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9320</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9460</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9020</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9320</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9460</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9180</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9940</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.0830</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9350</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.7350</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.7920</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.6190</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.7060</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.7740</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.6170</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.5670</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.5920</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3940</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>19/08/2026</x:t>
         </x:is>
       </x:c>
